--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2015/WISCONSIN_2015.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2015/WISCONSIN_2015.xlsx
@@ -2184,7 +2184,7 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Cuatro Cienegas</t>
+          <t>Cuatrocienegas</t>
         </is>
       </c>
       <c r="C102">
@@ -2940,7 +2940,7 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>General Simon Bolivar</t>
+          <t>Gral. Simon Bolivar</t>
         </is>
       </c>
       <c r="C144">
@@ -4009,7 +4009,7 @@
         <v>13</v>
       </c>
       <c r="D203">
-        <v>0.0009210060219624513</v>
+        <v>0.0009210060219624512</v>
       </c>
     </row>
     <row r="204">
@@ -4909,7 +4909,7 @@
         <v>13</v>
       </c>
       <c r="D253">
-        <v>0.0009210060219624513</v>
+        <v>0.0009210060219624512</v>
       </c>
     </row>
     <row r="254">
@@ -5226,7 +5226,7 @@
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>Dolores Hidalgo Cuna De La Independencia Nacional</t>
+          <t>Dolores Hidalgo</t>
         </is>
       </c>
       <c r="C271">
@@ -6169,7 +6169,7 @@
         <v>13</v>
       </c>
       <c r="D323">
-        <v>0.0009210060219624513</v>
+        <v>0.0009210060219624512</v>
       </c>
     </row>
     <row r="324">
@@ -8905,7 +8905,7 @@
         <v>13</v>
       </c>
       <c r="D475">
-        <v>0.0009210060219624513</v>
+        <v>0.0009210060219624512</v>
       </c>
     </row>
     <row r="476">
@@ -10597,7 +10597,7 @@
         <v>13</v>
       </c>
       <c r="D569">
-        <v>0.0009210060219624513</v>
+        <v>0.0009210060219624512</v>
       </c>
     </row>
     <row r="570">
@@ -11155,7 +11155,7 @@
         <v>13</v>
       </c>
       <c r="D600">
-        <v>0.0009210060219624513</v>
+        <v>0.0009210060219624512</v>
       </c>
     </row>
     <row r="601">
@@ -11904,7 +11904,7 @@
       </c>
       <c r="B642" t="inlineStr">
         <is>
-          <t>General Escobedo</t>
+          <t>Gral. Escobedo</t>
         </is>
       </c>
       <c r="C642">
@@ -12433,7 +12433,7 @@
         <v>13</v>
       </c>
       <c r="D671">
-        <v>0.0009210060219624513</v>
+        <v>0.0009210060219624512</v>
       </c>
     </row>
     <row r="672">
@@ -13722,7 +13722,7 @@
       </c>
       <c r="B743" t="inlineStr">
         <is>
-          <t>San Juan Mixtepec - Distr. 08 -</t>
+          <t>San Juan Mixtepec -Dto. 08 -</t>
         </is>
       </c>
       <c r="C743">
@@ -13740,7 +13740,7 @@
       </c>
       <c r="B744" t="inlineStr">
         <is>
-          <t>San Juan Mixtepec - Distr. 26 -</t>
+          <t>San Juan Mixtepec -Dto. 26 -</t>
         </is>
       </c>
       <c r="C744">
@@ -13801,7 +13801,7 @@
         <v>13</v>
       </c>
       <c r="D747">
-        <v>0.0009210060219624513</v>
+        <v>0.0009210060219624512</v>
       </c>
     </row>
     <row r="748">
@@ -14532,7 +14532,7 @@
       </c>
       <c r="B788" t="inlineStr">
         <is>
-          <t>San Pedro Mixtepec - Distr. 22 -</t>
+          <t>San Pedro Mixtepec -Dto. 22 -</t>
         </is>
       </c>
       <c r="C788">
@@ -15151,7 +15151,7 @@
         <v>13</v>
       </c>
       <c r="D822">
-        <v>0.0009210060219624513</v>
+        <v>0.0009210060219624512</v>
       </c>
     </row>
     <row r="823">
@@ -17545,7 +17545,7 @@
         <v>132</v>
       </c>
       <c r="D955">
-        <v>0.009351753453772583</v>
+        <v>0.009351753453772585</v>
       </c>
     </row>
     <row r="956">
@@ -21829,7 +21829,7 @@
         <v>132</v>
       </c>
       <c r="D1193">
-        <v>0.009351753453772583</v>
+        <v>0.009351753453772585</v>
       </c>
     </row>
     <row r="1194">
@@ -22441,7 +22441,7 @@
         <v>13</v>
       </c>
       <c r="D1227">
-        <v>0.0009210060219624513</v>
+        <v>0.0009210060219624512</v>
       </c>
     </row>
     <row r="1228">
@@ -22459,7 +22459,7 @@
         <v>13</v>
       </c>
       <c r="D1228">
-        <v>0.0009210060219624513</v>
+        <v>0.0009210060219624512</v>
       </c>
     </row>
     <row r="1229">
@@ -24457,7 +24457,7 @@
         <v>139</v>
       </c>
       <c r="D1339">
-        <v>0.009847679773290825</v>
+        <v>0.009847679773290824</v>
       </c>
     </row>
     <row r="1340">
@@ -24601,7 +24601,7 @@
         <v>13</v>
       </c>
       <c r="D1347">
-        <v>0.0009210060219624513</v>
+        <v>0.0009210060219624512</v>
       </c>
     </row>
     <row r="1348">
